--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B1F9C5-6319-40FE-A097-3480F90FAA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E1C758-93BA-492E-BE60-0D7730BB146A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="2832" windowWidth="17280" windowHeight="8964" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,8 @@
     <sheet name="Edition1" sheetId="2" r:id="rId5"/>
     <sheet name="Edition2" sheetId="3" r:id="rId6"/>
     <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
+    <sheet name="Program_App_Form" sheetId="8" r:id="rId8"/>
+    <sheet name="Standard_Assur_Form" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="38">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -70,19 +72,100 @@
   </si>
   <si>
     <t>Negotiation Initiated</t>
+  </si>
+  <si>
+    <t>fieldQuestion1__c</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>fieldQuestion2__c</t>
+  </si>
+  <si>
+    <t>Test2</t>
+  </si>
+  <si>
+    <t>fieldQuestion3__c</t>
+  </si>
+  <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>fieldQuestion4__c</t>
+  </si>
+  <si>
+    <t>Test4</t>
+  </si>
+  <si>
+    <t>fieldQuestion5__c</t>
+  </si>
+  <si>
+    <t>Test5</t>
+  </si>
+  <si>
+    <t>fieldQuestion6__c</t>
+  </si>
+  <si>
+    <t>Test6</t>
+  </si>
+  <si>
+    <t>fieldQuestion7__c</t>
+  </si>
+  <si>
+    <t>Test7</t>
+  </si>
+  <si>
+    <t>fieldQuestion8__c</t>
+  </si>
+  <si>
+    <t>Test8</t>
+  </si>
+  <si>
+    <t>fieldQuestion9__c</t>
+  </si>
+  <si>
+    <t>Test9</t>
+  </si>
+  <si>
+    <t>fieldQuestion10__c</t>
+  </si>
+  <si>
+    <t>Test10</t>
+  </si>
+  <si>
+    <t>fieldQuestion11__c</t>
+  </si>
+  <si>
+    <t>Test11</t>
+  </si>
+  <si>
+    <t>fieldAppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>Automation PM</t>
+  </si>
+  <si>
+    <t>fieldSubmittedOnForm__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,8 +188,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -722,4 +806,194 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC49C7FE-223D-4FBF-B645-D065CAF36E16}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B2EEDDD-7ADD-42BD-8D22-77348FEDB22F}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E1C758-93BA-492E-BE60-0D7730BB146A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9772474-6896-4E07-A806-26A74382F82A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="2832" windowWidth="17280" windowHeight="8964" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="3180" windowWidth="17280" windowHeight="8964" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
     <sheet name="Program_App_Form" sheetId="8" r:id="rId8"/>
     <sheet name="Standard_Assur_Form" sheetId="9" r:id="rId9"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -528,6 +529,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD63F744-BC8C-4A4B-91E1-AB4524DF7E1C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16224212-0054-4BAB-85AF-99AEA0A24F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442824C8-73A0-4AB4-88E7-A38DD6DBA069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -473,13 +473,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,18 +490,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -531,14 +531,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -560,7 +560,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -571,7 +571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -591,13 +591,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6328125" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +608,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -619,7 +619,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -630,7 +630,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -641,7 +641,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -660,13 +660,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -677,7 +677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -699,7 +699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -710,7 +710,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -721,7 +721,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -732,7 +732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -743,7 +743,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -765,7 +765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -787,7 +787,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -806,13 +806,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -823,7 +823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -834,7 +834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -853,13 +853,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -870,7 +870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -881,7 +881,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -892,7 +892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -912,13 +912,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -929,7 +929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -940,7 +940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -951,7 +951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -971,13 +971,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -988,7 +988,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -999,7 +999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1010,7 +1010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1051,13 +1051,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1079,7 +1079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1153,13 +1153,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1200,13 +1200,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1217,7 +1217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1247,14 +1247,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1306,14 +1306,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1324,7 +1324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442824C8-73A0-4AB4-88E7-A38DD6DBA069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D605598-C2C1-4383-8A9F-2D9D3182E2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +162,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -186,12 +192,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,7 +501,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C2">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LWC_New\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D605598-C2C1-4383-8A9F-2D9D3182E2BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DAAA93-632C-4F6D-AFFE-794468CFD420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -124,12 +124,6 @@
   </si>
   <si>
     <t>Overview: Application Overview</t>
-  </si>
-  <si>
-    <t>fieldNegotiationDueDate__c</t>
-  </si>
-  <si>
-    <t>fieldApplicationSectionsForRevision__c</t>
   </si>
   <si>
     <t>fieldExplanationOfRevisionsNeeded__c</t>
@@ -480,13 +474,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -497,7 +491,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -508,7 +502,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -519,7 +513,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -538,14 +532,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -556,34 +550,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
@@ -598,13 +592,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,7 +609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -626,7 +620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -637,7 +631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -648,12 +642,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>43707</v>
@@ -667,13 +661,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -684,7 +678,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -695,7 +689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -706,7 +700,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -717,7 +711,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -728,7 +722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -739,7 +733,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -750,7 +744,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -761,7 +755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -772,7 +766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -783,7 +777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -794,7 +788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -813,13 +807,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -830,7 +824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -841,7 +835,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -860,13 +854,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -877,34 +871,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -919,13 +913,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -936,7 +930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -947,7 +941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -958,12 +952,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>29</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -978,13 +972,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -995,56 +989,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C6">
         <v>43707</v>
@@ -1058,13 +1052,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1075,78 +1069,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C8">
         <v>43707</v>
@@ -1160,13 +1154,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1177,7 +1171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1207,13 +1201,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1224,7 +1218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1235,7 +1229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1254,14 +1248,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1272,7 +1266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1283,7 +1277,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1294,7 +1288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1313,14 +1307,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1331,18 +1325,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1353,12 +1347,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>43707</v>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DAAA93-632C-4F6D-AFFE-794468CFD420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC46B78-1A01-46A4-8E8B-6BF3D2609D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -78,67 +78,64 @@
     <t>Negotiation Initiated</t>
   </si>
   <si>
-    <t>fieldQuestion1__c</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
-    <t>fieldQuestion2__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion3__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion4__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion5__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion6__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion7__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion8__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion9__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion10__c</t>
-  </si>
-  <si>
-    <t>fieldQuestion11__c</t>
-  </si>
-  <si>
-    <t>fieldAppplicationSubmitted__c</t>
-  </si>
-  <si>
     <t>Automation PM</t>
   </si>
   <si>
-    <t>fieldSubmittedOnForm__c</t>
-  </si>
-  <si>
     <t>Overview: Application Overview</t>
   </si>
   <si>
-    <t>fieldExplanationOfRevisionsNeeded__c</t>
-  </si>
-  <si>
-    <t>fieldRevisionDueDate__c</t>
-  </si>
-  <si>
     <t>Overview Tab: Project Information</t>
   </si>
   <si>
-    <t>fieldPreApplicationSectionsforRevision__c</t>
-  </si>
-  <si>
     <t>Overview: Primary Place of Performance</t>
+  </si>
+  <si>
+    <t>PreApplicationSectionsforRevision__c</t>
+  </si>
+  <si>
+    <t>RevisionDueDate__c</t>
+  </si>
+  <si>
+    <t>AppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>SubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>Question1__c</t>
+  </si>
+  <si>
+    <t>Question2__c</t>
+  </si>
+  <si>
+    <t>Question3__c</t>
+  </si>
+  <si>
+    <t>Question4__c</t>
+  </si>
+  <si>
+    <t>Question5__c</t>
+  </si>
+  <si>
+    <t>Question6__c</t>
+  </si>
+  <si>
+    <t>Question7__c</t>
+  </si>
+  <si>
+    <t>Question8__c</t>
+  </si>
+  <si>
+    <t>Question9__c</t>
+  </si>
+  <si>
+    <t>Question10__c</t>
+  </si>
+  <si>
+    <t>Question11__c</t>
   </si>
 </sst>
 </file>
@@ -617,7 +614,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -683,10 +680,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -694,10 +691,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -705,10 +702,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -716,10 +713,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -727,10 +724,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -738,10 +735,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -749,10 +746,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -760,10 +757,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -771,10 +768,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -782,10 +779,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -793,10 +790,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -829,10 +826,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -840,7 +837,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -876,10 +873,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -887,7 +884,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -898,7 +895,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -1088,7 +1085,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1099,7 +1096,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC46B78-1A01-46A4-8E8B-6BF3D2609D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0489E801-D162-4324-A54B-CF7E8A2605FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -471,13 +471,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -499,7 +499,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -510,7 +510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -529,14 +529,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -558,7 +558,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -569,7 +569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -589,13 +589,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.6328125" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -617,7 +617,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -628,7 +628,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -639,7 +639,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -658,13 +658,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -686,7 +686,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -697,7 +697,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -708,7 +708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -719,7 +719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -730,7 +730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -741,7 +741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -752,7 +752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -763,7 +763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -774,7 +774,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -785,7 +785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -804,13 +804,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -832,7 +832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -851,13 +851,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -879,7 +879,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -890,7 +890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -910,13 +910,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -927,7 +927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -938,7 +938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -949,7 +949,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -969,13 +969,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -997,7 +997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1049,13 +1049,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1099,7 +1099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1151,13 +1151,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1179,7 +1179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1198,13 +1198,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.54296875" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1245,14 +1245,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1304,14 +1304,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1333,7 +1333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0489E801-D162-4324-A54B-CF7E8A2605FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB5BAFF-F2D3-4D63-9BCA-AD1911CB51A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19785" windowHeight="11760" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,28 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6604CB12-D3BC-47E1-B7B9-876A393BFDA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE3E5F35-5F51-4DCC-AA6B-1BB31CDDF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="15" windowWidth="20490" windowHeight="10920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="Edit_2" sheetId="6" r:id="rId2"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId3"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId5"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId6"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId7"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId8"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId9"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId10"/>
+    <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
+    <sheet name="Edition_PreApp" sheetId="11" r:id="rId2"/>
+    <sheet name="Edition" sheetId="1" r:id="rId3"/>
+    <sheet name="Edit_2" sheetId="6" r:id="rId4"/>
+    <sheet name="Edit_OverviewAll_options" sheetId="13" r:id="rId5"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId6"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId7"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId8"/>
+    <sheet name="Nego_Edit_Notes" sheetId="14" r:id="rId9"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId10"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId11"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId12"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId13"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="37">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -130,6 +134,21 @@
   </si>
   <si>
     <t>fieldExplanationOfRevisionsNeeded__c</t>
+  </si>
+  <si>
+    <t>fieldRevisionDueDate__c</t>
+  </si>
+  <si>
+    <t>Overview Tab: Project Information</t>
+  </si>
+  <si>
+    <t>fieldPreApplicationSectionsforRevision__c</t>
+  </si>
+  <si>
+    <t>Overview: Primary Place of Performance</t>
+  </si>
+  <si>
+    <t>Files: Notes</t>
   </si>
 </sst>
 </file>
@@ -171,9 +190,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,15 +475,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,34 +553,414 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="32.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>29</v>
+      <c r="B4" t="s">
+        <v>32</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -511,16 +972,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,26 +992,118 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>
@@ -558,16 +1111,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -578,7 +1131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -589,7 +1142,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -597,10 +1150,10 @@
         <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -608,28 +1161,50 @@
         <v>30</v>
       </c>
       <c r="C4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C6">
+      <c r="C8">
         <v>43707</v>
       </c>
     </row>
@@ -638,16 +1213,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +1233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -669,7 +1244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -685,16 +1260,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -705,7 +1280,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -716,7 +1291,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -732,17 +1307,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -753,7 +1328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -764,7 +1339,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -775,7 +1350,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -791,17 +1366,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4019BDBC-3FE0-4879-9A83-6BAE7622118A}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -812,29 +1386,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -842,127 +1416,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4">
-        <v>43707</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -971,152 +1428,6 @@
       </c>
       <c r="C5">
         <v>43707</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDB5BAFF-F2D3-4D63-9BCA-AD1911CB51A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2312B4E2-A2D4-4EB1-B6C9-DC3E23417FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\Product_LWC_20June\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2312B4E2-A2D4-4EB1-B6C9-DC3E23417FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B7D147-C73B-4FD5-A59F-58A1A2CEDFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>Question11__c</t>
+  </si>
+  <si>
+    <t>Forms and Files:Forms</t>
   </si>
 </sst>
 </file>
@@ -1330,7 +1333,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\Product_LWC_20June\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B7D147-C73B-4FD5-A59F-58A1A2CEDFE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9096D72E-309F-410D-ABC5-90DDD7C8A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -624,11 +624,11 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1121,7 +1121,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\Product_LWC_20June\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9096D72E-309F-410D-ABC5-90DDD7C8A88A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10406D02-7945-4D49-8072-ECA0E3FD5B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2312B4E2-A2D4-4EB1-B6C9-DC3E23417FBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F74ED92-3D67-4507-B195-D73133AFCFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -23,21 +23,33 @@
     <sheet name="Edition1" sheetId="2" r:id="rId8"/>
     <sheet name="Edition_Forms" sheetId="7" r:id="rId9"/>
     <sheet name="Edition2" sheetId="3" r:id="rId10"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId11"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId12"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId13"/>
+    <sheet name="Edition3" sheetId="14" r:id="rId11"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId12"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId13"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -136,6 +148,9 @@
   </si>
   <si>
     <t>Question11__c</t>
+  </si>
+  <si>
+    <t>Budget Tab: Budget Summary by Focus Area</t>
   </si>
 </sst>
 </file>
@@ -471,13 +486,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -488,7 +503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -499,7 +514,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -510,7 +525,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -529,14 +544,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,7 +562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -558,7 +573,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -569,7 +584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -587,15 +602,16 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCE8CED-1CCD-418D-A356-706E8695B457}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.77734375" customWidth="1"/>
+    <col min="3" max="3" width="47.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,18 +622,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -625,10 +641,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -636,18 +652,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5">
-        <v>43707</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -656,15 +661,84 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -686,7 +760,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -697,7 +771,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -708,7 +782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -719,7 +793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -730,7 +804,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -741,7 +815,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -752,7 +826,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -763,7 +837,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -774,7 +848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -785,7 +859,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -801,16 +875,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -821,7 +895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -832,7 +906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -851,13 +925,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -868,7 +942,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -879,7 +953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -890,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -910,13 +984,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -927,7 +1001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -938,7 +1012,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -949,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -969,13 +1043,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -986,7 +1060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -997,7 +1071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1008,7 +1082,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +1104,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1049,13 +1123,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1140,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1077,7 +1151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1088,7 +1162,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1099,7 +1173,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1110,7 +1184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1121,7 +1195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1132,7 +1206,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1151,13 +1225,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1179,7 +1253,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1198,13 +1272,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1245,14 +1319,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1263,7 +1337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1274,7 +1348,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1285,7 +1359,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1304,14 +1378,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1322,7 +1396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1333,7 +1407,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -5,27 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\Product_LWC_20June\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10406D02-7945-4D49-8072-ECA0E3FD5B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5951A82-CAE1-4AB6-98CF-0360AA28B39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
     <sheet name="Edition_PreApp" sheetId="11" r:id="rId2"/>
     <sheet name="Edition" sheetId="1" r:id="rId3"/>
-    <sheet name="Edit_2" sheetId="6" r:id="rId4"/>
-    <sheet name="Edit_OverviewAll_options" sheetId="13" r:id="rId5"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId6"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId7"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId8"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId9"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId10"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId11"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId12"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId13"/>
+    <sheet name="Nego_Edit_Notes" sheetId="14" r:id="rId4"/>
+    <sheet name="Edit_2" sheetId="6" r:id="rId5"/>
+    <sheet name="Edit_OverviewAll_options" sheetId="13" r:id="rId6"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId7"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId8"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId9"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId10"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId11"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId12"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId13"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId14"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -72,9 +73,6 @@
     <t>Overview: Project Information</t>
   </si>
   <si>
-    <t>Files: Forms</t>
-  </si>
-  <si>
     <t>Negotiation Initiated</t>
   </si>
   <si>
@@ -139,6 +137,9 @@
   </si>
   <si>
     <t>Forms and Files:Forms</t>
+  </si>
+  <si>
+    <t>Forms and Files: Notes</t>
   </si>
 </sst>
 </file>
@@ -474,13 +475,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -491,7 +492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -502,7 +503,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -513,7 +514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -521,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -530,16 +531,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -561,7 +621,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -572,7 +632,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -589,16 +649,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -617,10 +677,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -628,10 +688,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -639,10 +699,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -658,16 +718,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,125 +738,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -804,16 +864,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -824,23 +884,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -854,13 +914,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -871,18 +931,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -890,15 +950,15 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -913,13 +973,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -930,7 +990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -941,7 +1001,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -949,10 +1009,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -970,15 +1030,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB4716D-3E1A-43B9-862B-4AAAE94B4ADF}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +1049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -997,10 +1057,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1008,39 +1068,28 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C6">
+      <c r="C5">
         <v>43707</v>
       </c>
     </row>
@@ -1050,15 +1099,96 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1080,7 +1210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1088,10 +1218,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1099,10 +1229,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1113,7 +1243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1121,10 +1251,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1132,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1151,16 +1281,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1301,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +1312,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1198,16 +1328,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1218,7 +1348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1229,7 +1359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1245,17 +1375,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1277,7 +1407,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1288,7 +1418,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1297,65 +1427,6 @@
       </c>
       <c r="C4" t="s">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>43707</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5951A82-CAE1-4AB6-98CF-0360AA28B39B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC6087D-D062-4012-A0D5-0D64B290BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -62,9 +62,6 @@
   </si>
   <si>
     <t>Negoatiation Initiated</t>
-  </si>
-  <si>
-    <t>Attachments: Notes</t>
   </si>
   <si>
     <t>Budget: Budget Details</t>
@@ -511,7 +508,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -522,7 +519,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -559,7 +556,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -570,7 +567,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -629,7 +626,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -677,7 +674,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -688,7 +685,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -699,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -743,10 +740,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -754,10 +751,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -765,10 +762,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -776,10 +773,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -787,10 +784,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -798,10 +795,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -809,10 +806,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -820,10 +817,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -831,10 +828,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -842,10 +839,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -853,10 +850,10 @@
         <v>3</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -889,10 +886,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -900,7 +897,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -936,10 +933,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -950,7 +947,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -958,7 +955,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -998,7 +995,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1009,7 +1006,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1057,7 +1054,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1068,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1079,7 +1076,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1126,7 +1123,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1137,7 +1134,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1148,7 +1145,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1159,7 +1156,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1207,7 +1204,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1218,7 +1215,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1229,7 +1226,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1240,7 +1237,7 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1251,7 +1248,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1262,7 +1259,7 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1356,7 +1353,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1415,7 +1412,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\Product_LWC_20June\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10406D02-7945-4D49-8072-ECA0E3FD5B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70222757-67D2-4804-8192-DCA6BEC4D3C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>Overview: Project Information</t>
-  </si>
-  <si>
-    <t>Files: Forms</t>
   </si>
   <si>
     <t>Negotiation Initiated</t>
@@ -474,13 +471,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -491,7 +488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -502,7 +499,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -513,7 +510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -521,7 +518,7 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -532,14 +529,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,7 +547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -561,7 +558,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -572,7 +569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -592,13 +589,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="32.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -609,7 +606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -617,10 +614,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -628,10 +625,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -639,10 +636,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -661,13 +658,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,125 +675,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -807,13 +804,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -824,23 +821,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -854,13 +851,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -871,18 +868,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -890,15 +887,15 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4">
         <v>43707</v>
@@ -913,13 +910,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -930,7 +927,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -941,7 +938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -949,10 +946,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -972,13 +969,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1000,7 +997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1011,7 +1008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1019,10 +1016,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1030,10 +1027,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1052,13 +1049,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1069,7 +1066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1080,7 +1077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1088,10 +1085,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1099,10 +1096,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1113,7 +1110,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1121,10 +1118,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1132,10 +1129,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1154,13 +1151,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1171,7 +1168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +1179,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1201,13 +1198,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="48.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5546875" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1218,7 +1215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1229,7 +1226,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1248,14 +1245,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1277,7 +1274,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1288,7 +1285,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1307,14 +1304,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1325,7 +1322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1333,10 +1330,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1344,10 +1341,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC6087D-D062-4012-A0D5-0D64B290BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7624995-61D3-4C4D-B4C7-89B50D225FEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFC6087D-D062-4012-A0D5-0D64B290BD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1206392D-1D40-4DCA-860C-2DBB686FE4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
     <sheet name="Edition_PreApp" sheetId="11" r:id="rId2"/>
     <sheet name="Edition" sheetId="1" r:id="rId3"/>
-    <sheet name="Nego_Edit_Notes" sheetId="14" r:id="rId4"/>
-    <sheet name="Edit_2" sheetId="6" r:id="rId5"/>
-    <sheet name="Edit_OverviewAll_options" sheetId="13" r:id="rId6"/>
-    <sheet name="App Revision" sheetId="4" r:id="rId7"/>
-    <sheet name="Due Date" sheetId="5" r:id="rId8"/>
-    <sheet name="Edition1" sheetId="2" r:id="rId9"/>
-    <sheet name="Edition_Forms" sheetId="7" r:id="rId10"/>
-    <sheet name="Edition2" sheetId="3" r:id="rId11"/>
-    <sheet name="Ed_Over" sheetId="10" r:id="rId12"/>
-    <sheet name="Form_prog" sheetId="8" r:id="rId13"/>
-    <sheet name="Form_stand" sheetId="9" r:id="rId14"/>
+    <sheet name="Edition_Sanity" sheetId="15" r:id="rId4"/>
+    <sheet name="Nego_Edit_Notes" sheetId="14" r:id="rId5"/>
+    <sheet name="Edit_2" sheetId="6" r:id="rId6"/>
+    <sheet name="Edit_OverviewAll_options" sheetId="13" r:id="rId7"/>
+    <sheet name="App Revision" sheetId="4" r:id="rId8"/>
+    <sheet name="Due Date" sheetId="5" r:id="rId9"/>
+    <sheet name="Edition1" sheetId="2" r:id="rId10"/>
+    <sheet name="Edition_Forms" sheetId="7" r:id="rId11"/>
+    <sheet name="Edition2" sheetId="3" r:id="rId12"/>
+    <sheet name="Ed_Over" sheetId="10" r:id="rId13"/>
+    <sheet name="Form_prog" sheetId="8" r:id="rId14"/>
+    <sheet name="Form_stand" sheetId="9" r:id="rId15"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -528,6 +529,65 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -586,7 +646,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -646,7 +706,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -715,7 +775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -861,7 +921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -973,7 +1033,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1027,6 +1087,97 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A856D4-8C01-47D9-B906-24F9E40018C3}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB4716D-3E1A-43B9-862B-4AAAE94B4ADF}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1095,7 +1246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1176,7 +1327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1278,7 +1429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1325,7 +1476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1370,63 +1521,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1206392D-1D40-4DCA-860C-2DBB686FE4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89EEC78-D815-439D-9AA9-343DF2F6884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Forms and Files: Notes</t>
+  </si>
+  <si>
+    <t>Forms and Files: Forms</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89EEC78-D815-439D-9AA9-343DF2F6884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA60F67D-D2BE-4030-90FF-29ABB619063B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -1299,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1206392D-1D40-4DCA-860C-2DBB686FE4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA60F67D-D2BE-4030-90FF-29ABB619063B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Forms and Files: Notes</t>
+  </si>
+  <si>
+    <t>Forms and Files: Forms</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1296,7 +1299,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Va Qa Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1206392D-1D40-4DCA-860C-2DBB686FE4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD6B407-6FE3-4418-A183-3C45ADBD0B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1077,7 +1077,7 @@
         <v>4</v>
       </c>
       <c r="C4">
-        <v>43707</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA60F67D-D2BE-4030-90FF-29ABB619063B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90B57B8-296E-43CC-93EC-E5810AAAC9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="33">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -132,9 +132,6 @@
   </si>
   <si>
     <t>Question11__c</t>
-  </si>
-  <si>
-    <t>Forms and Files:Forms</t>
   </si>
   <si>
     <t>Forms and Files: Notes</t>
@@ -571,7 +568,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -619,7 +616,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -748,7 +745,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1208,7 +1205,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1219,7 +1216,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1299,7 +1296,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1402,7 +1399,7 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Negotiations_Field_Values.xlsx
+++ b/src/main/resources/Negotiations_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Product - LWC1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90B57B8-296E-43CC-93EC-E5810AAAC9C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E69FFD0-A3DD-426D-A28D-8A1EFE7D0FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="12" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="34">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Forms and Files: Forms</t>
+  </si>
+  <si>
+    <t>Forms and Files:Forms</t>
   </si>
 </sst>
 </file>
@@ -473,13 +476,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E6461C-092D-468A-A74C-060B2F9D630E}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -490,7 +493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -501,7 +504,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -512,7 +515,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -531,14 +534,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E8A2259-147F-4561-A3B1-EDF044621ED4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -560,7 +563,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -571,7 +574,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -590,14 +593,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE65BFC-6AFF-4E04-B5FE-B40621538AA3}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -608,7 +611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -616,10 +619,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -630,7 +633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -649,14 +652,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E8146D-F630-4D59-97ED-A466989510BA}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -667,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -678,7 +681,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -689,7 +692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -709,13 +712,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D512FFF-B9C9-4706-855F-11D2B48E7960}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+    <col min="2" max="2" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -726,7 +729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -737,7 +740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -748,7 +751,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -759,7 +762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -778,13 +781,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{719F51E6-A828-4383-8FA2-2267BCE3B3EF}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -795,7 +798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -806,7 +809,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -817,7 +820,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -828,7 +831,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -839,7 +842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -850,7 +853,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -861,7 +864,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -872,7 +875,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -883,7 +886,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -894,7 +897,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -905,7 +908,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -924,13 +927,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CBDAEE-3478-4244-A887-E57145794A99}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -941,7 +944,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -952,7 +955,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -971,13 +974,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4EA89F6-56A0-4A27-BD72-21B9653CC9D0}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -988,7 +991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -999,7 +1002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1010,7 +1013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1030,13 +1033,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1058,7 +1061,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1069,7 +1072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1089,13 +1092,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A856D4-8C01-47D9-B906-24F9E40018C3}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1117,7 +1120,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1128,7 +1131,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1139,7 +1142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1150,7 +1153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1161,7 +1164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1180,13 +1183,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBB4716D-3E1A-43B9-862B-4AAAE94B4ADF}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="35.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1219,7 +1222,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1230,7 +1233,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1249,13 +1252,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E662A116-3984-4CDE-8E67-B1843A9454D2}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1266,7 +1269,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1277,7 +1280,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1330,13 +1333,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{104AAD37-115F-4416-939F-E2B761EBC6C2}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1347,7 +1350,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1358,7 +1361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1369,7 +1372,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1391,7 +1394,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1402,7 +1405,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1413,7 +1416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1432,13 +1435,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA7FEAA1-1569-4FC1-85CC-6DA4026B11F4}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1449,7 +1452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1479,13 +1482,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C06C4F7E-796A-4AC4-AC16-D1680880C5DA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="48.5546875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1496,7 +1499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1507,7 +1510,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
